--- a/analisi_campione_1d_motivazione_apprezzamento.xlsx
+++ b/analisi_campione_1d_motivazione_apprezzamento.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,14 +462,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -488,14 +488,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Ospitalità</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -514,14 +514,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ospitalità</t>
+          <t>Città</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -540,14 +540,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>Percorsi Naturalistici</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -566,14 +566,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Città</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -592,14 +592,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Evento Sportivo</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -618,14 +618,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
@@ -644,14 +644,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
@@ -670,14 +670,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Persone</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -696,14 +696,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tutto</t>
+          <t>Poca Gente</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -722,14 +722,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Il Mare</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -748,14 +748,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Il Clima</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -774,14 +774,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La Natura E Il Cibo</t>
+          <t>Il Mare E La Tranquillità</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -800,14 +800,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Il Mae</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -826,14 +826,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>La Natura E La Cucina Sarda</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -852,14 +852,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Le Spiagge</t>
+          <t>L'Ospitalità E Il Mare</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -873,22 +873,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Il Mare E La Natura</t>
+          <t>Barumini E La Fondazione Che La Gestisce</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -899,22 +899,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Il Mare E La Tranquillità</t>
+          <t>Il Paesaggio</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -925,22 +925,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Il Paesaggio E Il Cibo</t>
+          <t>La Gente E L'Ospitalità</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -951,22 +951,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La Cucina Sarda E La Cordialità Dei Sardi</t>
+          <t>La Natura E La Cucina Sarda</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
         <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -982,17 +982,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>La Tranquillità</t>
+          <t>La Natura E Orgosolo</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Il Paesaggio E L'Aria Pulita</t>
+          <t>La Tranquillità Dei Luoghi</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
         <v>6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>Man Nuoro</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cortesia</t>
+          <t>Museo Nivola</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Silenzio</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1096,7 +1096,7 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tranquillità</t>
+          <t>La Sardegna Rende Felici</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1122,7 +1122,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1133,22 +1133,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accoglienza In Tutta L'Isola</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Barumini E La Fondazione Che La Gestisce</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1174,7 +1174,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>I Sardi</t>
+          <t>Bellezza Paesaggi</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Il Mare E Il Clima</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1226,7 +1226,7 @@
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>La Città Di Cagliari</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spiagge</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Panorami</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -1320,17 +1320,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Serenità</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Persone</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1382,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Relax</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1419,22 +1419,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tranquillità</t>
+          <t>Il Mare</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
         <v>4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1445,22 +1445,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>L'Affetto Degli Amici E La Loro Ospitalità</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -1471,22 +1471,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>I Parcheggi</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Ospitalità</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1528,17 +1528,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>Relax</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1554,199 +1554,199 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Relax</t>
+          <t>Tranquillità</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ospitalità</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Amici</t>
+          <t>Calma</t>
         </is>
       </c>
       <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
         <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>10</v>
-      </c>
-      <c r="F47" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Camminate</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Persone</t>
+          <t>Cibo Fresco</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tradizioni</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Il Mare</t>
+          <t>Cucina Locale</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>La Spiaggia E Gli Edifici Di Cagliari</t>
         </is>
       </c>
       <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
         <v>8</v>
-      </c>
-      <c r="E52" t="n">
-        <v>25</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Ospitalità</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -1814,17 +1814,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spiagge</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
         <v>10</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1835,22 +1835,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Il Mare</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1861,22 +1861,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Calma</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1887,22 +1887,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>I Sardi</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>La Cucina Sarda</t>
+          <t>I Sardi E Il Cibo</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -1939,22 +1939,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Panorami</t>
+          <t>Le Spiagge E Il Mare</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="n">
         <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sentieri</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -1991,22 +1991,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gente</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Il Clima</t>
+          <t>Il Clima E La Spiaggia</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2048,17 +2048,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>L'Architettura Della Città Di Cagliari</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2074,17 +2074,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>L'Architettura Della Città Di Cagliari</t>
+          <t>La Città Di Cagliari In Generale</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="n">
         <v>4</v>
-      </c>
-      <c r="F64" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2100,17 +2100,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>L'Atmosfera Della Città Di Cagliari</t>
+          <t>Le Città</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -2121,22 +2121,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Città Vecchia</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2147,22 +2147,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Barumini</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Città</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Amici</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2214,7 +2214,7 @@
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Il Clima E La Spiaggia</t>
+          <t>Panorami</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2240,7 +2240,7 @@
         <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Il Clima E Le Spiagge</t>
+          <t>Relax</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2266,7 +2266,7 @@
         <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -2282,17 +2282,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Spazi Liberi Non Affollati</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Tutto</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
         <v>8</v>
-      </c>
-      <c r="F73" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2355,22 +2355,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Il Mare</t>
+          <t>Accoglienza Della Città</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2381,22 +2381,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Grotte Di Nettuno</t>
+          <t>Bellezza Del Mare</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spiagge</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="n">
         <v>4</v>
-      </c>
-      <c r="F77" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spiagge Libere</t>
+          <t>Il Mare E Le Spiagge</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>La Città Di Cagliari</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -2485,48 +2485,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atmosfera</t>
+          <t>Persone</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Cibo Locale</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2540,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2588,14 +2562,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -2614,14 +2588,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Ospitalità</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2640,14 +2614,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ospitalità</t>
+          <t>Città</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -2666,14 +2640,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>Percorsi Naturalistici</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -2692,14 +2666,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Città</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -2718,14 +2692,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Evento Sportivo</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -2744,14 +2718,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
@@ -2770,14 +2744,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
@@ -2796,14 +2770,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Persone</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -2822,14 +2796,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tutto</t>
+          <t>Poca Gente</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -2848,14 +2822,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Percorsi Naturalistici</t>
+          <t>Sole</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -2874,14 +2848,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>I Sardi E Il Paesaggio</t>
+          <t>Vino</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -2895,22 +2869,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Il Mare</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2921,12 +2895,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Accoglienza</t>
+          <t>Il Clima</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2936,7 +2910,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2947,12 +2921,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Il Mare E La Tranquillità</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2962,7 +2936,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2973,12 +2947,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L'Ospitalità</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2988,7 +2962,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2999,22 +2973,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paesaggio Urbano</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -3025,22 +2999,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poca Gente</t>
+          <t>L'Ospitalità E Il Mare</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -3051,12 +3025,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Relax</t>
+          <t>Barumini E La Fondazione Che La Gestisce</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3066,7 +3040,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3077,12 +3051,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sole</t>
+          <t>Il Paesaggio</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3092,7 +3066,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -3103,12 +3077,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vino</t>
+          <t>La Gente E L'Ospitalità</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3118,7 +3092,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3129,22 +3103,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ATTIVO O SPORTIVO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>I Colori Della Città E La Natura</t>
+          <t>La Natura E La Cucina Sarda</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -3155,22 +3129,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Il Mare</t>
+          <t>La Natura E Orgosolo</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -3181,22 +3155,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>La Tranquillità Dei Luoghi</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
         <v>6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -3207,22 +3181,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>La Natura E Il Cibo</t>
+          <t>Man Nuoro</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -3233,22 +3207,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Il Mae</t>
+          <t>Museo Nivola</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -3259,22 +3233,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>La Natura E La Cucina Sarda</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3285,22 +3259,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Le Spiagge</t>
+          <t>La Sardegna Rende Felici</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -3311,22 +3285,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Il Mare E La Natura</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -3337,22 +3311,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Il Mare E La Tranquillità</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
         <v>4</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -3363,22 +3337,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Il Paesaggio E Il Cibo</t>
+          <t>Bellezza Paesaggi</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -3389,22 +3363,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La Cucina Sarda E La Cordialità Dei Sardi</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -3415,22 +3389,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>La Cultura Sarda</t>
+          <t>La Città Di Cagliari</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -3441,22 +3415,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Il Mare E Le Spiagge</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3467,12 +3441,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Il Clima</t>
+          <t>Panorami</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -3482,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -3493,12 +3467,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Il Clima E L'Ospitalità</t>
+          <t>Serenità</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -3508,7 +3482,7 @@
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -3519,12 +3493,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Il Paesaggio E La Tranquillità</t>
+          <t>Spiagge</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -3534,7 +3508,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -3545,12 +3519,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BALNEARE</t>
+          <t>RURALE E NATURALISTICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>Tranquillità</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -3560,7 +3534,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -3571,19 +3545,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>La Tranquillità</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -3597,19 +3571,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Il Paesaggio E L'Aria Pulita</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -3623,19 +3597,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>Accoglienza</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -3649,19 +3623,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cortesia</t>
+          <t>Il Mare</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
@@ -3675,19 +3649,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Silenzio</t>
+          <t>L'Affetto Degli Amici E La Loro Ospitalità</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -3701,19 +3675,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tranquillità</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
@@ -3727,12 +3701,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Accoglienza In Tutta L'Isola</t>
+          <t>Ospitalità</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -3753,12 +3727,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Barumini E La Fondazione Che La Gestisce</t>
+          <t>Relax</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -3779,12 +3753,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>I Sardi</t>
+          <t>Tranquillità</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -3800,69 +3774,69 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Il Mare E Il Clima</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Il Mare E La Cucina Sarda</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Il Paesaggio</t>
+          <t>Calma</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3872,23 +3846,23 @@
         <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>La Città Di Cagliari</t>
+          <t>Camminate</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3898,23 +3872,23 @@
         <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>La Gente E L'Ospitalità</t>
+          <t>Cibo Fresco</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3924,23 +3898,23 @@
         <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>La Gentilezza Dei Sardi</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -3950,23 +3924,23 @@
         <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>La Natura</t>
+          <t>Cucina Locale</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3976,23 +3950,23 @@
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>La Natura E La Cucina Sarda</t>
+          <t>La Spiaggia E Gli Edifici Di Cagliari</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -4002,23 +3976,23 @@
         <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>La Natura E Orgosolo</t>
+          <t>Ospitalità</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -4028,23 +4002,23 @@
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>La Tranquillità Dei Luoghi</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -4054,23 +4028,23 @@
         <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Man Nuoro</t>
+          <t>Paesaggi Naturali</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -4080,23 +4054,23 @@
         <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Museo Nivola</t>
+          <t>Persone</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -4106,325 +4080,325 @@
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>ATTIVO O SPORTIVO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cibo</t>
+          <t>Tranquillità</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spiagge</t>
+          <t>Il Mare</t>
         </is>
       </c>
       <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
         <v>4</v>
       </c>
-      <c r="E62" t="n">
-        <v>21</v>
-      </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
         <v>4</v>
       </c>
-      <c r="E63" t="n">
-        <v>10</v>
-      </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>I Sardi</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>I Sardi E Il Cibo</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="n">
         <v>4</v>
-      </c>
-      <c r="F65" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Persone</t>
+          <t>Le Spiagge E Il Mare</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>BALNEARE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Relax</t>
+          <t>Paesaggi</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tranquillità</t>
+          <t>Clima</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paesaggi</t>
+          <t>Il Clima E La Spiaggia</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>I Parcheggi</t>
+          <t>L'Architettura Della Città Di Cagliari</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Il Cielo Limpido E L'Aria Buona</t>
+          <t>La Città Di Cagliari In Generale</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tutto</t>
+          <t>Le Città</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4434,23 +4408,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gentilezza</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4460,23 +4434,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Organizzazione Servizi</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F74" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4486,23 +4460,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Persone Ospitali</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
         <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4512,23 +4486,23 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>La Sardegna Rende Felici</t>
+          <t>Amici</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4538,7 +4512,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Accoglienza</t>
+          <t>Panorami</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -4548,13 +4522,13 @@
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4564,7 +4538,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ambiente</t>
+          <t>Relax</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -4574,13 +4548,13 @@
         <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4590,7 +4564,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atmosfera</t>
+          <t>Spazi Liberi Non Affollati</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -4600,13 +4574,13 @@
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4616,7 +4590,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bellezza Dei Luoghi Nella Natura</t>
+          <t>Tutto</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -4626,49 +4600,49 @@
         <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bellezza Paesaggi</t>
+          <t>Mare</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Calette</t>
+          <t>Accoglienza Della Città</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -4678,23 +4652,23 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Bellezza Del Mare</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -4704,23 +4678,23 @@
         <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>La Città Di Cagliari</t>
+          <t>Cibo</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -4730,23 +4704,23 @@
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Paesaggio</t>
+          <t>Il Mare E Le Spiagge</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -4756,23 +4730,23 @@
         <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Panorami</t>
+          <t>La Città Di Cagliari</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -4782,23 +4756,23 @@
         <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ITALIANI</t>
+          <t>STRANIERI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RURALE E NATURALISTICO</t>
+          <t>VISITA A PARENTI E/O AMICI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serenità</t>
+          <t>Persone</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4808,2789 +4782,7 @@
         <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Il Buon Cibo</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>L'Ospitalità E Il Clima</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>La Cucina Sarda</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Soprattutto Il Pesce</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Strade In Modo</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Mare</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="n">
-        <v>34</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Cibo</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>9</v>
-      </c>
-      <c r="E94" t="n">
-        <v>18</v>
-      </c>
-      <c r="F94" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Relax</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>4</v>
-      </c>
-      <c r="E95" t="n">
-        <v>11</v>
-      </c>
-      <c r="F95" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ospitalità</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>4</v>
-      </c>
-      <c r="E96" t="n">
-        <v>9</v>
-      </c>
-      <c r="F96" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Paesaggi</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>3</v>
-      </c>
-      <c r="E97" t="n">
-        <v>12</v>
-      </c>
-      <c r="F97" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Amici</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>3</v>
-      </c>
-      <c r="E98" t="n">
-        <v>10</v>
-      </c>
-      <c r="F98" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Natura</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>3</v>
-      </c>
-      <c r="E99" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Persone</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>2</v>
-      </c>
-      <c r="E100" t="n">
-        <v>8</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Tradizioni</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>2</v>
-      </c>
-      <c r="E101" t="n">
-        <v>7</v>
-      </c>
-      <c r="F101" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Il Mare</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="n">
-        <v>6</v>
-      </c>
-      <c r="F102" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Cucina Tipica</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>2</v>
-      </c>
-      <c r="E103" t="n">
-        <v>4</v>
-      </c>
-      <c r="F103" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Rivedere La Famiglia</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>2</v>
-      </c>
-      <c r="E104" t="n">
-        <v>4</v>
-      </c>
-      <c r="F104" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Accoglienza</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F105" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Clima</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>2</v>
-      </c>
-      <c r="E106" t="n">
-        <v>3</v>
-      </c>
-      <c r="F106" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Spiagge</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>2</v>
-      </c>
-      <c r="E107" t="n">
-        <v>3</v>
-      </c>
-      <c r="F107" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Tutto</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>2</v>
-      </c>
-      <c r="E108" t="n">
-        <v>3</v>
-      </c>
-      <c r="F108" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Bellezza Posti</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>2</v>
-      </c>
-      <c r="E109" t="n">
-        <v>2</v>
-      </c>
-      <c r="F109" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Poco Urbanizzata</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>6</v>
-      </c>
-      <c r="F110" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Rurale</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" t="n">
-        <v>6</v>
-      </c>
-      <c r="F111" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Cibo Genuino</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" t="n">
-        <v>5</v>
-      </c>
-      <c r="F112" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Cibo Tradizionale</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" t="n">
-        <v>4</v>
-      </c>
-      <c r="F113" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Visita Parenti</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" t="n">
-        <v>4</v>
-      </c>
-      <c r="F114" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Autenticità</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" t="n">
-        <v>2</v>
-      </c>
-      <c r="F115" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Bellezze Paesaggistiche</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="n">
-        <v>2</v>
-      </c>
-      <c r="F116" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Borghi</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" t="n">
-        <v>2</v>
-      </c>
-      <c r="F117" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Divertimento</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" t="n">
-        <v>2</v>
-      </c>
-      <c r="F118" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Enogastronomia</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" t="n">
-        <v>2</v>
-      </c>
-      <c r="F119" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>L'Affetto Degli Amici E La Loro Ospitalità</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="n">
-        <v>2</v>
-      </c>
-      <c r="F120" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ospitalità E Calore Delle Persone</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="n">
-        <v>2</v>
-      </c>
-      <c r="F121" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Paesaggio</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" t="n">
-        <v>2</v>
-      </c>
-      <c r="F122" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Spiagge E Tranquillità</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" t="n">
-        <v>2</v>
-      </c>
-      <c r="F123" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Tempo Trascorso Con Amici</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" t="n">
-        <v>2</v>
-      </c>
-      <c r="F124" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Tranquillità</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" t="n">
-        <v>2</v>
-      </c>
-      <c r="F125" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Visita Amici E Parenti</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2</v>
-      </c>
-      <c r="F126" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Bellezza Del Paesaggio</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Compagnia</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Cultura</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Essere Ospite Dagli Amici</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>La Famiglia</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Pace</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>ITALIANI</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>VISITA A PARENTI E/O AMICI</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Silenzio</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Natura</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>8</v>
-      </c>
-      <c r="E134" t="n">
-        <v>25</v>
-      </c>
-      <c r="F134" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Mare</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>5</v>
-      </c>
-      <c r="E135" t="n">
-        <v>17</v>
-      </c>
-      <c r="F135" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Spiagge</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" t="n">
-        <v>10</v>
-      </c>
-      <c r="F136" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Clima</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>2</v>
-      </c>
-      <c r="E137" t="n">
-        <v>7</v>
-      </c>
-      <c r="F137" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Calma</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>2</v>
-      </c>
-      <c r="E138" t="n">
-        <v>6</v>
-      </c>
-      <c r="F138" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Paesaggi</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>2</v>
-      </c>
-      <c r="E139" t="n">
-        <v>6</v>
-      </c>
-      <c r="F139" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>La Cucina Sarda</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>5</v>
-      </c>
-      <c r="F140" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Panorami</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
-        <v>5</v>
-      </c>
-      <c r="F141" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Sentieri</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>5</v>
-      </c>
-      <c r="F142" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Gente</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>4</v>
-      </c>
-      <c r="F143" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Città</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="n">
-        <v>3</v>
-      </c>
-      <c r="F144" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Escursione</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>3</v>
-      </c>
-      <c r="F145" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Gentilezza Delle Persone</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>3</v>
-      </c>
-      <c r="F146" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Percorsi Naturalistici</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="n">
-        <v>3</v>
-      </c>
-      <c r="F147" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Bellezza</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>2</v>
-      </c>
-      <c r="F148" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Camminate</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>2</v>
-      </c>
-      <c r="F149" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Cucina Locale</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>2</v>
-      </c>
-      <c r="F150" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Fare Windsurf Al Poetto</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>2</v>
-      </c>
-      <c r="F151" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>La Natura</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2</v>
-      </c>
-      <c r="F152" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Persone</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>2</v>
-      </c>
-      <c r="F153" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Sicurezza</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>2</v>
-      </c>
-      <c r="F154" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Stile Di Vita Tranquillo</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-      <c r="F155" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>ATTIVO O SPORTIVO</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Tranquillità</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Il Clima</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>3</v>
-      </c>
-      <c r="E157" t="n">
-        <v>6</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Cibo</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>2</v>
-      </c>
-      <c r="E158" t="n">
-        <v>5</v>
-      </c>
-      <c r="F158" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>L'Architettura Della Città Di Cagliari</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>2</v>
-      </c>
-      <c r="E159" t="n">
-        <v>4</v>
-      </c>
-      <c r="F159" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>L'Atmosfera Della Città Di Cagliari</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" t="n">
-        <v>4</v>
-      </c>
-      <c r="F160" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Città Vecchia</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" t="n">
-        <v>3</v>
-      </c>
-      <c r="F161" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Barumini</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" t="n">
-        <v>2</v>
-      </c>
-      <c r="F162" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Città</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" t="n">
-        <v>2</v>
-      </c>
-      <c r="F163" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Clima</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Il Clima E La Spiaggia</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Il Clima E Le Spiagge</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>L'Archeologia E La Città Di Alghero</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>La Città Di Cagliari</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>La Città Di Cagliari In Generale</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" t="n">
-        <v>2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>La Cucina Sarda E I Sardi</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" t="n">
-        <v>2</v>
-      </c>
-      <c r="F170" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>La Cucina Sarda E La Città Di Cagliari</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" t="n">
-        <v>2</v>
-      </c>
-      <c r="F171" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>La Natura E La Cultura Sarda</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" t="n">
-        <v>2</v>
-      </c>
-      <c r="F172" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>La Tranquillità E La Città Di Cagliari</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" t="n">
-        <v>2</v>
-      </c>
-      <c r="F173" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Lavori Scavi</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" t="n">
-        <v>2</v>
-      </c>
-      <c r="F174" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Le Città</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" t="n">
-        <v>2</v>
-      </c>
-      <c r="F175" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Le Spiagge E L'Architettura Delle Città</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" t="n">
-        <v>2</v>
-      </c>
-      <c r="F176" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Le Spiagge E La Città Di Cagliari</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Mare</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" t="n">
-        <v>2</v>
-      </c>
-      <c r="F178" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Vino</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>L'Architettura Della Città Di Cagliari E Il Paesaggio</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" t="n">
-        <v>1</v>
-      </c>
-      <c r="F180" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>CULTURALE - MUSEALE (ARTISTICO E ARCHITETTONICO)</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>La Cultura Sarda E La Spiaggia Del Poetto</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1</v>
-      </c>
-      <c r="F181" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Mare</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>3</v>
-      </c>
-      <c r="E182" t="n">
-        <v>10</v>
-      </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Natura</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>2</v>
-      </c>
-      <c r="E183" t="n">
-        <v>8</v>
-      </c>
-      <c r="F183" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Paesaggi</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>2</v>
-      </c>
-      <c r="E184" t="n">
-        <v>6</v>
-      </c>
-      <c r="F184" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Il Mare</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>2</v>
-      </c>
-      <c r="E185" t="n">
-        <v>4</v>
-      </c>
-      <c r="F185" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Grotte Di Nettuno</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" t="n">
-        <v>4</v>
-      </c>
-      <c r="F186" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Spiagge</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" t="n">
-        <v>4</v>
-      </c>
-      <c r="F187" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Spiagge Libere</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" t="n">
-        <v>4</v>
-      </c>
-      <c r="F188" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Tempo</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>1</v>
-      </c>
-      <c r="E189" t="n">
-        <v>4</v>
-      </c>
-      <c r="F189" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Atmosfera</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>1</v>
-      </c>
-      <c r="E190" t="n">
-        <v>3</v>
-      </c>
-      <c r="F190" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Cibo Locale</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>1</v>
-      </c>
-      <c r="E191" t="n">
-        <v>3</v>
-      </c>
-      <c r="F191" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Persone</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" t="n">
-        <v>3</v>
-      </c>
-      <c r="F192" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Spazi Liberi Non Affollati</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>1</v>
-      </c>
-      <c r="E193" t="n">
-        <v>2</v>
-      </c>
-      <c r="F193" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>STRANIERI</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>RURALE E NATURALISTICO</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Tutto</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E194" t="n">
-        <v>2</v>
-      </c>
-      <c r="F194" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
